--- a/finance-controlling/FB75-customer-credit-memo.xlsx
+++ b/finance-controlling/FB75-customer-credit-memo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/24a7865e3124cb3d/Documents/PostNow/github-templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/24a7865e3124cb3d/Documents/PostNow/github-templates/finance-controlling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_FBE209F5A48EC06889FF6FE448B231014C21C46A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C1811BD-E172-48A5-A20A-65EA557345B8}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="11_FBE209F5A48EC06889FF6FE448B231014C21C46A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C035CADC-17FC-44FB-B14B-487976A003C5}"/>
   <bookViews>
-    <workbookView xWindow="3820" yWindow="3110" windowWidth="11610" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="5" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="How It Works" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Template!$A$5:$W$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Template!$A$5:$V$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Template!$5:$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -297,23 +297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Debit Credit Ind
-Applies to: D row
-S debit on a credit memo, the reverse of an invoice.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+    <comment ref="Q5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -330,7 +314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
+    <comment ref="R5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
         <r>
           <rPr>
@@ -346,7 +330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
+    <comment ref="S5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
         <r>
           <rPr>
@@ -362,7 +346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
+    <comment ref="T5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
       <text>
         <r>
           <rPr>
@@ -378,7 +362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
       <text>
         <r>
           <rPr>
@@ -394,7 +378,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
       <text>
         <r>
           <rPr>
@@ -415,7 +399,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="256">
   <si>
     <t>FB75   Customer Credit Memo</t>
   </si>
@@ -477,9 +461,6 @@
     <t>GL Account *</t>
   </si>
   <si>
-    <t>Debit Credit Ind *</t>
-  </si>
-  <si>
     <t>Amount *</t>
   </si>
   <si>
@@ -525,9 +506,6 @@
     <t>CN-2026-0011</t>
   </si>
   <si>
-    <t>795.00</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -546,15 +524,9 @@
     <t>0000800000</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
     <t>600.00</t>
   </si>
   <si>
-    <t>A1</t>
-  </si>
-  <si>
     <t>PC-1000</t>
   </si>
   <si>
@@ -591,9 +563,6 @@
     <t>CN-2026-0012</t>
   </si>
   <si>
-    <t>349.80</t>
-  </si>
-  <si>
     <t>Goodwill credit</t>
   </si>
   <si>
@@ -630,9 +599,6 @@
     <t>•  Populate the invoice reference where the credit relates to a specific invoice. It is what makes clearing straightforward later.</t>
   </si>
   <si>
-    <t>•  Amounts stay positive. The debit credit indicator carries the direction.</t>
-  </si>
-  <si>
     <t>Every column</t>
   </si>
   <si>
@@ -723,9 +689,6 @@
     <t>CURRENCYAMOUNT-AMT_DOCCUR</t>
   </si>
   <si>
-    <t>Total credit including tax.</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
@@ -765,18 +728,9 @@
     <t>The revenue being reversed.  [text format]</t>
   </si>
   <si>
-    <t>Debit Credit Ind</t>
-  </si>
-  <si>
-    <t>S debit on a credit memo, the reverse of an invoice.  [text format]</t>
-  </si>
-  <si>
     <t>Amount</t>
   </si>
   <si>
-    <t>Always positive here.</t>
-  </si>
-  <si>
     <t>ACCOUNTGL-TAX_CODE</t>
   </si>
   <si>
@@ -843,9 +797,6 @@
     <t>ACCOUNTTAX</t>
   </si>
   <si>
-    <t>Tax lines, where tax is passed explicitly rather than calculated.</t>
-  </si>
-  <si>
     <t>CURRENCYAMOUNT</t>
   </si>
   <si>
@@ -936,9 +887,6 @@
     <t>The revenue being reversed.</t>
   </si>
   <si>
-    <t>S debit on a credit memo, the reverse of an invoice.</t>
-  </si>
-  <si>
     <t>TAX_CODE</t>
   </si>
   <si>
@@ -966,9 +914,6 @@
     <t>Sign, not indicator</t>
   </si>
   <si>
-    <t>The screen uses a posting key to decide debit or credit. The BAPI uses the sign of AMT_DOCCUR. A credit is a negative amount. This template keeps amounts positive and applies the sign from the S/H column, which is why that column exists.</t>
-  </si>
-  <si>
     <t>BUS_ACT</t>
   </si>
   <si>
@@ -1167,9 +1112,6 @@
     <t>Start your 14 day free trial at postnow.ai</t>
   </si>
   <si>
-    <t>Template provided free by PostNow.ai. All sample data is fictional. Validate field requirements against your own configuration before a production load.</t>
-  </si>
-  <si>
     <t>Customer Credit Memo</t>
   </si>
   <si>
@@ -1191,7 +1133,40 @@
     <t>https://postnow.ai/templates/finance-controlling</t>
   </si>
   <si>
-    <t>Sheets: Template (enter your data), Field Guide, BAPI Mapping, How It Works. Mandatory columns have a dark green heading and an asterisk. Sample data is fictional.</t>
+    <t>-750.00</t>
+  </si>
+  <si>
+    <t>-330.00</t>
+  </si>
+  <si>
+    <t>•  Amounts carry the sign. Enter the Gross Amount (the customer line) as a negative amount, a credit, and the revenue lines being reversed as positive amounts, debits. The customer line and the lines of one credit memo must add up to zero, or SAP rejects the document with message F5 702 (balance in transaction currency).</t>
+  </si>
+  <si>
+    <t>The customer line. Enter it as a negative amount, a credit. It and the lines of the credit memo must add up to zero, including any tax line.</t>
+  </si>
+  <si>
+    <t>Signed: the revenue lines being reversed are positive, debits. With the negative Gross Amount, the credit memo adds up to zero.</t>
+  </si>
+  <si>
+    <t>Leave blank unless you also pass a tax line. See Before you load.  [text format]</t>
+  </si>
+  <si>
+    <t>•  Tax is not calculated for you. BAPI_ACC_DOCUMENT_POST has no "calculate tax" option: tax is a line of its own in ACCOUNTTAX, with its amount in CURRENCYAMOUNT. This template has no tax line, so the samples carry no tax code and the Gross Amount equals the sum of the lines.</t>
+  </si>
+  <si>
+    <t>Leave blank unless you also pass a tax line in ACCOUNTTAX.</t>
+  </si>
+  <si>
+    <t>Tax lines. BAPI_ACC_DOCUMENT_POST does not calculate tax: a tax amount is passed as its own line here, with its amount in CURRENCYAMOUNT. This template has no tax columns.</t>
+  </si>
+  <si>
+    <t>The screen uses a posting key to decide debit or credit. The BAPI uses the sign of AMT_DOCCUR: a debit is a positive amount, a credit is a negative amount. Enter credits as negative amounts in this template. If the lines do not add up to zero, SAP rejects the document with message F5 702.</t>
+  </si>
+  <si>
+    <t>Sheets: Template (enter your data), Field Guide, BAPI Mapping, How It Works. Mandatory columns have a dark green heading and an asterisk.</t>
+  </si>
+  <si>
+    <t>Template provided free by PostNow.ai. Validate field requirements against your own configuration before a production load.</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1381,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1448,6 +1423,12 @@
         <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1477,7 +1458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1506,32 +1487,6 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -1541,6 +1496,11 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -1560,35 +1520,20 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1597,14 +1542,62 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2046,6 +2039,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2335,47 +2332,47 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="30.6328125" style="51" customWidth="1"/>
-    <col min="3" max="3" width="70.6328125" style="51" customWidth="1"/>
+    <col min="2" max="2" width="30.6328125" style="16" customWidth="1"/>
+    <col min="3" max="3" width="70.6328125" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="26" x14ac:dyDescent="0.65">
-      <c r="B2" s="48" t="s">
-        <v>251</v>
+      <c r="B2" s="13" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B4" s="49" t="s">
-        <v>252</v>
-      </c>
-      <c r="C4" s="51" t="s">
-        <v>253</v>
+      <c r="B4" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B7" s="15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B8" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B10" s="14" t="s">
         <v>254</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B7" s="50" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B8" s="49" t="s">
-        <v>256</v>
-      </c>
-      <c r="C8" s="52" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B10" s="49" t="s">
-        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -2392,7 +2389,7 @@
     <tabColor rgb="FF1E8E4E"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2409,124 +2406,119 @@
     <col min="14" max="14" width="17" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="13" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="19" customWidth="1"/>
-    <col min="21" max="21" width="17" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="20" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="19" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:22" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-    </row>
-    <row r="2" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+    </row>
+    <row r="2" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-    </row>
-    <row r="3" spans="1:23" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="27" t="s">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+    </row>
+    <row r="3" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-    </row>
-    <row r="4" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="31" t="s">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+    </row>
+    <row r="4" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-    </row>
-    <row r="5" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+    </row>
+    <row r="5" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -2578,7 +2570,7 @@
       <c r="Q5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="S5" s="2" t="s">
@@ -2593,140 +2585,133 @@
       <c r="V5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:22" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="Q6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="R6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="S6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="T6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="U6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="V6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="W6" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="I7" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="K7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="L7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="N7" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="5"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
+      <c r="U7" s="6"/>
       <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-    </row>
-    <row r="8" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>30</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -2741,39 +2726,34 @@
       <c r="M8" s="8"/>
       <c r="N8" s="9"/>
       <c r="O8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="R8" s="8"/>
+      <c r="S8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q8" s="8" t="s">
+      <c r="T8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="U8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="S8" s="8" t="s">
+      <c r="V8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="T8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="W8" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -2788,88 +2768,82 @@
       <c r="M9" s="5"/>
       <c r="N9" s="6"/>
       <c r="O9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T9" s="5"/>
+      <c r="U9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="V9" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="C10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Q9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R9" s="6" t="s">
+      <c r="E10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="S9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U9" s="5"/>
-      <c r="V9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="W9" s="6" t="s">
+      <c r="F10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>58</v>
+      <c r="I10" s="40" t="s">
+        <v>245</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="8"/>
       <c r="S10" s="8"/>
       <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
+      <c r="U10" s="9"/>
       <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-    </row>
-    <row r="11" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -2884,37 +2858,32 @@
       <c r="M11" s="5"/>
       <c r="N11" s="6"/>
       <c r="O11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="Q11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="V11" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="W11" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -2929,38 +2898,33 @@
       <c r="M12" s="8"/>
       <c r="N12" s="9"/>
       <c r="O12" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>63</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="R12" s="8"/>
       <c r="S12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="T12" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="U12" s="8"/>
+        <v>42</v>
+      </c>
+      <c r="T12" s="8"/>
+      <c r="U12" s="9" t="s">
+        <v>56</v>
+      </c>
       <c r="V12" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="W12" s="9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:W12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:V12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="4">
-    <mergeCell ref="A3:W3"/>
-    <mergeCell ref="A2:W2"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A3:V3"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A4:V4"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:B400">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -2972,17 +2936,14 @@
       <formula>AND($A7="H",C7="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O7:R400">
+  <conditionalFormatting sqref="O7:Q400">
     <cfRule type="expression" dxfId="0" priority="11">
       <formula>AND($A7="D",O7="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" errorTitle="Not a valid entry" error="Pick a value from the list." sqref="A7:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"H,D"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Not a valid entry" error="Pick a value from the list." sqref="Q7:Q400" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"S,H"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" errorTitle="Not a valid entry" error="Pick a value from the list." sqref="J7:J400" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"USD,EUR,GBP,CAD,AUD,JPY,INR"</formula1>
@@ -3016,544 +2977,536 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+    </row>
+    <row r="2" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+    </row>
+    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-    </row>
-    <row r="2" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+    </row>
+    <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-    </row>
-    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="33" t="s">
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+    </row>
+    <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-    </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="32" t="s">
+      <c r="B12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-    </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="32" t="s">
+      <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="32" t="s">
+      <c r="D12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-    </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="32" t="s">
+      <c r="E12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-    </row>
-    <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="33" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-    </row>
-    <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="B13" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="D13" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="E13" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="1" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="B14" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="50" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="B15" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="E15" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="14" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="46" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="15" t="s">
+      <c r="B16" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="18" t="s">
+      <c r="E16" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="19" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="41" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+      <c r="B17" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="E17" s="45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="50"/>
+    </row>
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="17" t="s">
+      <c r="D27" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="D28" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="17" t="s">
+      <c r="D29" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="12" t="s">
+      <c r="D30" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" s="56" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="17" t="s">
+      <c r="D31" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="45" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D32" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="50" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="C33" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="17" t="s">
+      <c r="D33" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" s="45"/>
+    </row>
+    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="19"/>
-    </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="21" t="s">
+      <c r="D34" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E34" s="50"/>
+    </row>
+    <row r="36" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="24" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="10" t="s">
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28" s="14" t="s">
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="23" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="15" t="s">
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" s="19" t="s">
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="23" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="20" t="s">
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="21" t="s">
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="E31" s="19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" s="19"/>
-    </row>
-    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E34" s="14"/>
-    </row>
-    <row r="36" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-    </row>
-    <row r="37" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-    </row>
-    <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-    </row>
-    <row r="39" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-    </row>
-    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-    </row>
-    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-    </row>
-    <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="A1:E1"/>
@@ -3568,7 +3521,8 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3579,7 +3533,7 @@
   <sheetPr>
     <tabColor rgb="FF0F766E"/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="26" customWidth="1"/>
@@ -3588,619 +3542,604 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+    </row>
+    <row r="2" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+    </row>
+    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-    </row>
-    <row r="2" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+      <c r="B9" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-    </row>
-    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="33" t="s">
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-    </row>
-    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-    </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="24" t="s">
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+    </row>
+    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-    </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-    </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-    </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-    </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-    </row>
-    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-    </row>
-    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
     </row>
     <row r="15" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="45"/>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="50"/>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="D22" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="1" t="s">
+    </row>
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D23" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="50" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="51" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="13" t="s">
+      <c r="D24" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="52" t="s">
         <v>153</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" s="14" t="s">
+      <c r="D25" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="50"/>
+    </row>
+    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="51" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="19" t="s">
+      <c r="D26" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="45"/>
+    </row>
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="52" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="20" t="s">
+      <c r="D27" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D28" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="45" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="50"/>
+    </row>
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D19" s="17" t="s">
+      <c r="E30" s="45"/>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="19"/>
-    </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="12" t="s">
+      <c r="E31" s="50" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D21" s="17" t="s">
+      <c r="E32" s="53" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="D22" s="12" t="s">
+      <c r="E33" s="56" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="D23" s="17" t="s">
+      <c r="E34" s="45"/>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="D24" s="12" t="s">
+      <c r="E35" s="50"/>
+    </row>
+    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="17" t="s">
+      <c r="E36" s="45"/>
+    </row>
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="19"/>
-    </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="14"/>
-    </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C28" s="20" t="s">
+      <c r="E37" s="50"/>
+    </row>
+    <row r="39" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="14" t="s">
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="11" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="C29" s="21" t="s">
+      <c r="B40" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="19"/>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="20" t="s">
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+    </row>
+    <row r="41" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="14"/>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" s="21" t="s">
+      <c r="B41" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+    </row>
+    <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31" s="19" t="s">
+      <c r="B42" s="25" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="14" t="s">
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+    </row>
+    <row r="43" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="11" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="C34" s="20" t="s">
+      <c r="B43" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" s="14"/>
-    </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="21" t="s">
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+    </row>
+    <row r="44" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="19"/>
-    </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="C36" s="20" t="s">
+      <c r="B44" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="D36" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="14"/>
-    </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C37" s="21" t="s">
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+    </row>
+    <row r="45" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D37" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="19"/>
-    </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" s="20" t="s">
+      <c r="B45" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="D38" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" s="14"/>
-    </row>
-    <row r="40" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="33" t="s">
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+    </row>
+    <row r="46" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-    </row>
-    <row r="41" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="25" t="s">
+      <c r="B46" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="B41" s="35" t="s">
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+    </row>
+    <row r="48" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-    </row>
-    <row r="42" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="B42" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-    </row>
-    <row r="43" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="B43" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-    </row>
-    <row r="44" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="B44" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-    </row>
-    <row r="45" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="B45" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-    </row>
-    <row r="46" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="B46" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-    </row>
-    <row r="47" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="B47" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-    </row>
-    <row r="49" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="B9:E9"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A48:E48"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B46:E46"/>
     <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B46:E46"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B8:E8"/>
     <mergeCell ref="B43:E43"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="B9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4228,203 +4167,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
+      <c r="A1" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
+      <c r="A2" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
+      <c r="A3" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
     </row>
     <row r="5" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="47" t="s">
-        <v>198</v>
-      </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
+      <c r="A9" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
     </row>
     <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
+      <c r="A11" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C12" s="44" t="s">
-        <v>200</v>
-      </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
+      <c r="C12" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="44" t="s">
-        <v>203</v>
-      </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="40" t="s">
-        <v>205</v>
-      </c>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
+      <c r="C13" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="26"/>
+      <c r="E13" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
     </row>
     <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
+      <c r="A15" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
     </row>
     <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="26">
+      <c r="B16" s="12">
         <v>1</v>
       </c>
-      <c r="C16" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
+      <c r="C16" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
     </row>
     <row r="17" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
+      <c r="C17" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
     </row>
     <row r="19" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="26">
+      <c r="B19" s="12">
         <v>2</v>
       </c>
-      <c r="C19" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
+      <c r="C19" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
     </row>
     <row r="20" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C20" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
+      <c r="C20" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
     </row>
     <row r="21" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4446,46 +4385,46 @@
     <row r="38" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="2:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
+      <c r="C40" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
     </row>
     <row r="42" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="26">
+      <c r="B42" s="12">
         <v>3</v>
       </c>
-      <c r="C42" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
+      <c r="C42" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
     </row>
     <row r="43" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C43" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
+      <c r="C43" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
     </row>
     <row r="44" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4512,46 +4451,46 @@
     <row r="66" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="67" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="68" spans="2:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C68" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="D68" s="28"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28"/>
-      <c r="J68" s="28"/>
-      <c r="K68" s="28"/>
+      <c r="C68" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19"/>
+      <c r="K68" s="19"/>
     </row>
     <row r="70" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="26">
+      <c r="B70" s="12">
         <v>4</v>
       </c>
-      <c r="C70" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
+      <c r="C70" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="19"/>
     </row>
     <row r="71" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C71" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="D71" s="28"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="28"/>
-      <c r="J71" s="28"/>
-      <c r="K71" s="28"/>
+      <c r="C71" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="19"/>
     </row>
     <row r="72" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="73" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4578,46 +4517,46 @@
     <row r="94" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="95" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="96" spans="3:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C96" s="39" t="s">
-        <v>217</v>
-      </c>
-      <c r="D96" s="28"/>
-      <c r="E96" s="28"/>
-      <c r="F96" s="28"/>
-      <c r="G96" s="28"/>
-      <c r="H96" s="28"/>
-      <c r="I96" s="28"/>
-      <c r="J96" s="28"/>
-      <c r="K96" s="28"/>
+      <c r="C96" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="D96" s="19"/>
+      <c r="E96" s="19"/>
+      <c r="F96" s="19"/>
+      <c r="G96" s="19"/>
+      <c r="H96" s="19"/>
+      <c r="I96" s="19"/>
+      <c r="J96" s="19"/>
+      <c r="K96" s="19"/>
     </row>
     <row r="98" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="26">
+      <c r="B98" s="12">
         <v>5</v>
       </c>
-      <c r="C98" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="D98" s="28"/>
-      <c r="E98" s="28"/>
-      <c r="F98" s="28"/>
-      <c r="G98" s="28"/>
-      <c r="H98" s="28"/>
-      <c r="I98" s="28"/>
-      <c r="J98" s="28"/>
-      <c r="K98" s="28"/>
+      <c r="C98" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D98" s="19"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="19"/>
+      <c r="G98" s="19"/>
+      <c r="H98" s="19"/>
+      <c r="I98" s="19"/>
+      <c r="J98" s="19"/>
+      <c r="K98" s="19"/>
     </row>
     <row r="99" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="D99" s="28"/>
-      <c r="E99" s="28"/>
-      <c r="F99" s="28"/>
-      <c r="G99" s="28"/>
-      <c r="H99" s="28"/>
-      <c r="I99" s="28"/>
-      <c r="J99" s="28"/>
-      <c r="K99" s="28"/>
+      <c r="C99" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="D99" s="19"/>
+      <c r="E99" s="19"/>
+      <c r="F99" s="19"/>
+      <c r="G99" s="19"/>
+      <c r="H99" s="19"/>
+      <c r="I99" s="19"/>
+      <c r="J99" s="19"/>
+      <c r="K99" s="19"/>
     </row>
     <row r="100" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="101" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4644,46 +4583,46 @@
     <row r="122" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="123" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="124" spans="2:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C124" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="D124" s="28"/>
-      <c r="E124" s="28"/>
-      <c r="F124" s="28"/>
-      <c r="G124" s="28"/>
-      <c r="H124" s="28"/>
-      <c r="I124" s="28"/>
-      <c r="J124" s="28"/>
-      <c r="K124" s="28"/>
+      <c r="C124" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="D124" s="19"/>
+      <c r="E124" s="19"/>
+      <c r="F124" s="19"/>
+      <c r="G124" s="19"/>
+      <c r="H124" s="19"/>
+      <c r="I124" s="19"/>
+      <c r="J124" s="19"/>
+      <c r="K124" s="19"/>
     </row>
     <row r="126" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B126" s="26">
+      <c r="B126" s="12">
         <v>6</v>
       </c>
-      <c r="C126" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="D126" s="28"/>
-      <c r="E126" s="28"/>
-      <c r="F126" s="28"/>
-      <c r="G126" s="28"/>
-      <c r="H126" s="28"/>
-      <c r="I126" s="28"/>
-      <c r="J126" s="28"/>
-      <c r="K126" s="28"/>
+      <c r="C126" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="D126" s="19"/>
+      <c r="E126" s="19"/>
+      <c r="F126" s="19"/>
+      <c r="G126" s="19"/>
+      <c r="H126" s="19"/>
+      <c r="I126" s="19"/>
+      <c r="J126" s="19"/>
+      <c r="K126" s="19"/>
     </row>
     <row r="127" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C127" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="D127" s="28"/>
-      <c r="E127" s="28"/>
-      <c r="F127" s="28"/>
-      <c r="G127" s="28"/>
-      <c r="H127" s="28"/>
-      <c r="I127" s="28"/>
-      <c r="J127" s="28"/>
-      <c r="K127" s="28"/>
+      <c r="C127" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="D127" s="19"/>
+      <c r="E127" s="19"/>
+      <c r="F127" s="19"/>
+      <c r="G127" s="19"/>
+      <c r="H127" s="19"/>
+      <c r="I127" s="19"/>
+      <c r="J127" s="19"/>
+      <c r="K127" s="19"/>
     </row>
     <row r="128" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="129" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4710,46 +4649,46 @@
     <row r="150" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="151" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="152" spans="2:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C152" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="D152" s="28"/>
-      <c r="E152" s="28"/>
-      <c r="F152" s="28"/>
-      <c r="G152" s="28"/>
-      <c r="H152" s="28"/>
-      <c r="I152" s="28"/>
-      <c r="J152" s="28"/>
-      <c r="K152" s="28"/>
+      <c r="C152" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="D152" s="19"/>
+      <c r="E152" s="19"/>
+      <c r="F152" s="19"/>
+      <c r="G152" s="19"/>
+      <c r="H152" s="19"/>
+      <c r="I152" s="19"/>
+      <c r="J152" s="19"/>
+      <c r="K152" s="19"/>
     </row>
     <row r="154" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B154" s="26">
+      <c r="B154" s="12">
         <v>7</v>
       </c>
-      <c r="C154" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="D154" s="28"/>
-      <c r="E154" s="28"/>
-      <c r="F154" s="28"/>
-      <c r="G154" s="28"/>
-      <c r="H154" s="28"/>
-      <c r="I154" s="28"/>
-      <c r="J154" s="28"/>
-      <c r="K154" s="28"/>
+      <c r="C154" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="D154" s="19"/>
+      <c r="E154" s="19"/>
+      <c r="F154" s="19"/>
+      <c r="G154" s="19"/>
+      <c r="H154" s="19"/>
+      <c r="I154" s="19"/>
+      <c r="J154" s="19"/>
+      <c r="K154" s="19"/>
     </row>
     <row r="155" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C155" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D155" s="28"/>
-      <c r="E155" s="28"/>
-      <c r="F155" s="28"/>
-      <c r="G155" s="28"/>
-      <c r="H155" s="28"/>
-      <c r="I155" s="28"/>
-      <c r="J155" s="28"/>
-      <c r="K155" s="28"/>
+      <c r="C155" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="D155" s="19"/>
+      <c r="E155" s="19"/>
+      <c r="F155" s="19"/>
+      <c r="G155" s="19"/>
+      <c r="H155" s="19"/>
+      <c r="I155" s="19"/>
+      <c r="J155" s="19"/>
+      <c r="K155" s="19"/>
     </row>
     <row r="156" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="157" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4767,46 +4706,46 @@
     <row r="169" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="170" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="171" spans="2:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C171" s="39" t="s">
-        <v>226</v>
-      </c>
-      <c r="D171" s="28"/>
-      <c r="E171" s="28"/>
-      <c r="F171" s="28"/>
-      <c r="G171" s="28"/>
-      <c r="H171" s="28"/>
-      <c r="I171" s="28"/>
-      <c r="J171" s="28"/>
-      <c r="K171" s="28"/>
+      <c r="C171" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="D171" s="19"/>
+      <c r="E171" s="19"/>
+      <c r="F171" s="19"/>
+      <c r="G171" s="19"/>
+      <c r="H171" s="19"/>
+      <c r="I171" s="19"/>
+      <c r="J171" s="19"/>
+      <c r="K171" s="19"/>
     </row>
     <row r="173" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B173" s="26">
+      <c r="B173" s="12">
         <v>8</v>
       </c>
-      <c r="C173" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="D173" s="28"/>
-      <c r="E173" s="28"/>
-      <c r="F173" s="28"/>
-      <c r="G173" s="28"/>
-      <c r="H173" s="28"/>
-      <c r="I173" s="28"/>
-      <c r="J173" s="28"/>
-      <c r="K173" s="28"/>
+      <c r="C173" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="D173" s="19"/>
+      <c r="E173" s="19"/>
+      <c r="F173" s="19"/>
+      <c r="G173" s="19"/>
+      <c r="H173" s="19"/>
+      <c r="I173" s="19"/>
+      <c r="J173" s="19"/>
+      <c r="K173" s="19"/>
     </row>
     <row r="174" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C174" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="D174" s="28"/>
-      <c r="E174" s="28"/>
-      <c r="F174" s="28"/>
-      <c r="G174" s="28"/>
-      <c r="H174" s="28"/>
-      <c r="I174" s="28"/>
-      <c r="J174" s="28"/>
-      <c r="K174" s="28"/>
+      <c r="C174" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="D174" s="19"/>
+      <c r="E174" s="19"/>
+      <c r="F174" s="19"/>
+      <c r="G174" s="19"/>
+      <c r="H174" s="19"/>
+      <c r="I174" s="19"/>
+      <c r="J174" s="19"/>
+      <c r="K174" s="19"/>
     </row>
     <row r="175" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="176" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4823,46 +4762,46 @@
     <row r="187" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="188" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="189" spans="2:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C189" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="D189" s="28"/>
-      <c r="E189" s="28"/>
-      <c r="F189" s="28"/>
-      <c r="G189" s="28"/>
-      <c r="H189" s="28"/>
-      <c r="I189" s="28"/>
-      <c r="J189" s="28"/>
-      <c r="K189" s="28"/>
+      <c r="C189" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="D189" s="19"/>
+      <c r="E189" s="19"/>
+      <c r="F189" s="19"/>
+      <c r="G189" s="19"/>
+      <c r="H189" s="19"/>
+      <c r="I189" s="19"/>
+      <c r="J189" s="19"/>
+      <c r="K189" s="19"/>
     </row>
     <row r="191" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B191" s="26">
+      <c r="B191" s="12">
         <v>9</v>
       </c>
-      <c r="C191" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="D191" s="28"/>
-      <c r="E191" s="28"/>
-      <c r="F191" s="28"/>
-      <c r="G191" s="28"/>
-      <c r="H191" s="28"/>
-      <c r="I191" s="28"/>
-      <c r="J191" s="28"/>
-      <c r="K191" s="28"/>
+      <c r="C191" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="D191" s="19"/>
+      <c r="E191" s="19"/>
+      <c r="F191" s="19"/>
+      <c r="G191" s="19"/>
+      <c r="H191" s="19"/>
+      <c r="I191" s="19"/>
+      <c r="J191" s="19"/>
+      <c r="K191" s="19"/>
     </row>
     <row r="192" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C192" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="D192" s="28"/>
-      <c r="E192" s="28"/>
-      <c r="F192" s="28"/>
-      <c r="G192" s="28"/>
-      <c r="H192" s="28"/>
-      <c r="I192" s="28"/>
-      <c r="J192" s="28"/>
-      <c r="K192" s="28"/>
+      <c r="C192" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="D192" s="19"/>
+      <c r="E192" s="19"/>
+      <c r="F192" s="19"/>
+      <c r="G192" s="19"/>
+      <c r="H192" s="19"/>
+      <c r="I192" s="19"/>
+      <c r="J192" s="19"/>
+      <c r="K192" s="19"/>
     </row>
     <row r="193" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="194" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4889,46 +4828,46 @@
     <row r="215" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="216" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="217" spans="2:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C217" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="D217" s="28"/>
-      <c r="E217" s="28"/>
-      <c r="F217" s="28"/>
-      <c r="G217" s="28"/>
-      <c r="H217" s="28"/>
-      <c r="I217" s="28"/>
-      <c r="J217" s="28"/>
-      <c r="K217" s="28"/>
+      <c r="C217" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="D217" s="19"/>
+      <c r="E217" s="19"/>
+      <c r="F217" s="19"/>
+      <c r="G217" s="19"/>
+      <c r="H217" s="19"/>
+      <c r="I217" s="19"/>
+      <c r="J217" s="19"/>
+      <c r="K217" s="19"/>
     </row>
     <row r="219" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B219" s="26">
+      <c r="B219" s="12">
         <v>10</v>
       </c>
-      <c r="C219" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="D219" s="28"/>
-      <c r="E219" s="28"/>
-      <c r="F219" s="28"/>
-      <c r="G219" s="28"/>
-      <c r="H219" s="28"/>
-      <c r="I219" s="28"/>
-      <c r="J219" s="28"/>
-      <c r="K219" s="28"/>
+      <c r="C219" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="D219" s="19"/>
+      <c r="E219" s="19"/>
+      <c r="F219" s="19"/>
+      <c r="G219" s="19"/>
+      <c r="H219" s="19"/>
+      <c r="I219" s="19"/>
+      <c r="J219" s="19"/>
+      <c r="K219" s="19"/>
     </row>
     <row r="220" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C220" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="D220" s="28"/>
-      <c r="E220" s="28"/>
-      <c r="F220" s="28"/>
-      <c r="G220" s="28"/>
-      <c r="H220" s="28"/>
-      <c r="I220" s="28"/>
-      <c r="J220" s="28"/>
-      <c r="K220" s="28"/>
+      <c r="C220" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="D220" s="19"/>
+      <c r="E220" s="19"/>
+      <c r="F220" s="19"/>
+      <c r="G220" s="19"/>
+      <c r="H220" s="19"/>
+      <c r="I220" s="19"/>
+      <c r="J220" s="19"/>
+      <c r="K220" s="19"/>
     </row>
     <row r="221" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="222" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4949,58 +4888,58 @@
     <row r="237" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="238" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="239" spans="3:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C239" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="D239" s="28"/>
-      <c r="E239" s="28"/>
-      <c r="F239" s="28"/>
-      <c r="G239" s="28"/>
-      <c r="H239" s="28"/>
-      <c r="I239" s="28"/>
-      <c r="J239" s="28"/>
-      <c r="K239" s="28"/>
+      <c r="C239" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="D239" s="19"/>
+      <c r="E239" s="19"/>
+      <c r="F239" s="19"/>
+      <c r="G239" s="19"/>
+      <c r="H239" s="19"/>
+      <c r="I239" s="19"/>
+      <c r="J239" s="19"/>
+      <c r="K239" s="19"/>
     </row>
     <row r="241" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="B241" s="28"/>
-      <c r="C241" s="28"/>
-      <c r="D241" s="28"/>
-      <c r="E241" s="28"/>
-      <c r="F241" s="28"/>
-      <c r="G241" s="28"/>
-      <c r="H241" s="28"/>
-      <c r="I241" s="28"/>
-      <c r="J241" s="28"/>
-      <c r="K241" s="28"/>
+      <c r="A241" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="B241" s="19"/>
+      <c r="C241" s="19"/>
+      <c r="D241" s="19"/>
+      <c r="E241" s="19"/>
+      <c r="F241" s="19"/>
+      <c r="G241" s="19"/>
+      <c r="H241" s="19"/>
+      <c r="I241" s="19"/>
+      <c r="J241" s="19"/>
+      <c r="K241" s="19"/>
     </row>
     <row r="242" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C242" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D242" s="28"/>
-      <c r="E242" s="28"/>
-      <c r="F242" s="28"/>
-      <c r="G242" s="28"/>
-      <c r="H242" s="28"/>
-      <c r="I242" s="28"/>
-      <c r="J242" s="28"/>
-      <c r="K242" s="28"/>
+      <c r="C242" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="D242" s="19"/>
+      <c r="E242" s="19"/>
+      <c r="F242" s="19"/>
+      <c r="G242" s="19"/>
+      <c r="H242" s="19"/>
+      <c r="I242" s="19"/>
+      <c r="J242" s="19"/>
+      <c r="K242" s="19"/>
     </row>
     <row r="243" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C243" s="32" t="s">
-        <v>238</v>
-      </c>
-      <c r="D243" s="28"/>
-      <c r="E243" s="28"/>
-      <c r="F243" s="28"/>
-      <c r="G243" s="28"/>
-      <c r="H243" s="28"/>
-      <c r="I243" s="28"/>
-      <c r="J243" s="28"/>
-      <c r="K243" s="28"/>
+      <c r="C243" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="D243" s="19"/>
+      <c r="E243" s="19"/>
+      <c r="F243" s="19"/>
+      <c r="G243" s="19"/>
+      <c r="H243" s="19"/>
+      <c r="I243" s="19"/>
+      <c r="J243" s="19"/>
+      <c r="K243" s="19"/>
     </row>
     <row r="244" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="245" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -5027,43 +4966,43 @@
     <row r="266" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="267" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="268" spans="3:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C268" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="D268" s="28"/>
-      <c r="E268" s="28"/>
-      <c r="F268" s="28"/>
-      <c r="G268" s="28"/>
-      <c r="H268" s="28"/>
-      <c r="I268" s="28"/>
-      <c r="J268" s="28"/>
-      <c r="K268" s="28"/>
+      <c r="C268" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="D268" s="19"/>
+      <c r="E268" s="19"/>
+      <c r="F268" s="19"/>
+      <c r="G268" s="19"/>
+      <c r="H268" s="19"/>
+      <c r="I268" s="19"/>
+      <c r="J268" s="19"/>
+      <c r="K268" s="19"/>
     </row>
     <row r="270" spans="3:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C270" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="D270" s="28"/>
-      <c r="E270" s="28"/>
-      <c r="F270" s="28"/>
-      <c r="G270" s="28"/>
-      <c r="H270" s="28"/>
-      <c r="I270" s="28"/>
-      <c r="J270" s="28"/>
-      <c r="K270" s="28"/>
+      <c r="C270" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="D270" s="19"/>
+      <c r="E270" s="19"/>
+      <c r="F270" s="19"/>
+      <c r="G270" s="19"/>
+      <c r="H270" s="19"/>
+      <c r="I270" s="19"/>
+      <c r="J270" s="19"/>
+      <c r="K270" s="19"/>
     </row>
     <row r="271" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C271" s="32" t="s">
-        <v>241</v>
-      </c>
-      <c r="D271" s="28"/>
-      <c r="E271" s="28"/>
-      <c r="F271" s="28"/>
-      <c r="G271" s="28"/>
-      <c r="H271" s="28"/>
-      <c r="I271" s="28"/>
-      <c r="J271" s="28"/>
-      <c r="K271" s="28"/>
+      <c r="C271" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D271" s="19"/>
+      <c r="E271" s="19"/>
+      <c r="F271" s="19"/>
+      <c r="G271" s="19"/>
+      <c r="H271" s="19"/>
+      <c r="I271" s="19"/>
+      <c r="J271" s="19"/>
+      <c r="K271" s="19"/>
     </row>
     <row r="272" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="273" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -5086,157 +5025,143 @@
     <row r="290" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="291" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="292" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C292" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="D292" s="28"/>
-      <c r="E292" s="28"/>
-      <c r="F292" s="28"/>
-      <c r="G292" s="28"/>
-      <c r="H292" s="28"/>
-      <c r="I292" s="28"/>
-      <c r="J292" s="28"/>
-      <c r="K292" s="28"/>
+      <c r="C292" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="D292" s="19"/>
+      <c r="E292" s="19"/>
+      <c r="F292" s="19"/>
+      <c r="G292" s="19"/>
+      <c r="H292" s="19"/>
+      <c r="I292" s="19"/>
+      <c r="J292" s="19"/>
+      <c r="K292" s="19"/>
     </row>
     <row r="294" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A294" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="B294" s="28"/>
-      <c r="C294" s="28"/>
-      <c r="D294" s="28"/>
-      <c r="E294" s="28"/>
-      <c r="F294" s="28"/>
-      <c r="G294" s="28"/>
-      <c r="H294" s="28"/>
-      <c r="I294" s="28"/>
-      <c r="J294" s="28"/>
-      <c r="K294" s="28"/>
+      <c r="A294" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B294" s="19"/>
+      <c r="C294" s="19"/>
+      <c r="D294" s="19"/>
+      <c r="E294" s="19"/>
+      <c r="F294" s="19"/>
+      <c r="G294" s="19"/>
+      <c r="H294" s="19"/>
+      <c r="I294" s="19"/>
+      <c r="J294" s="19"/>
+      <c r="K294" s="19"/>
     </row>
     <row r="295" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B295" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="C295" s="28"/>
-      <c r="D295" s="28"/>
-      <c r="E295" s="28"/>
-      <c r="F295" s="28"/>
-      <c r="G295" s="28"/>
-      <c r="H295" s="28"/>
-      <c r="I295" s="28"/>
-      <c r="J295" s="28"/>
-      <c r="K295" s="28"/>
+      <c r="B295" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="C295" s="19"/>
+      <c r="D295" s="19"/>
+      <c r="E295" s="19"/>
+      <c r="F295" s="19"/>
+      <c r="G295" s="19"/>
+      <c r="H295" s="19"/>
+      <c r="I295" s="19"/>
+      <c r="J295" s="19"/>
+      <c r="K295" s="19"/>
     </row>
     <row r="296" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B296" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="C296" s="28"/>
-      <c r="D296" s="28"/>
-      <c r="E296" s="28"/>
-      <c r="F296" s="28"/>
-      <c r="G296" s="28"/>
-      <c r="H296" s="28"/>
-      <c r="I296" s="28"/>
-      <c r="J296" s="28"/>
-      <c r="K296" s="28"/>
+      <c r="B296" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="C296" s="19"/>
+      <c r="D296" s="19"/>
+      <c r="E296" s="19"/>
+      <c r="F296" s="19"/>
+      <c r="G296" s="19"/>
+      <c r="H296" s="19"/>
+      <c r="I296" s="19"/>
+      <c r="J296" s="19"/>
+      <c r="K296" s="19"/>
     </row>
     <row r="297" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B297" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="C297" s="28"/>
-      <c r="D297" s="28"/>
-      <c r="E297" s="28"/>
-      <c r="F297" s="28"/>
-      <c r="G297" s="28"/>
-      <c r="H297" s="28"/>
-      <c r="I297" s="28"/>
-      <c r="J297" s="28"/>
-      <c r="K297" s="28"/>
+      <c r="B297" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="C297" s="19"/>
+      <c r="D297" s="19"/>
+      <c r="E297" s="19"/>
+      <c r="F297" s="19"/>
+      <c r="G297" s="19"/>
+      <c r="H297" s="19"/>
+      <c r="I297" s="19"/>
+      <c r="J297" s="19"/>
+      <c r="K297" s="19"/>
     </row>
     <row r="298" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B298" s="32" t="s">
-        <v>247</v>
-      </c>
-      <c r="C298" s="28"/>
-      <c r="D298" s="28"/>
-      <c r="E298" s="28"/>
-      <c r="F298" s="28"/>
-      <c r="G298" s="28"/>
-      <c r="H298" s="28"/>
-      <c r="I298" s="28"/>
-      <c r="J298" s="28"/>
-      <c r="K298" s="28"/>
+      <c r="B298" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="C298" s="19"/>
+      <c r="D298" s="19"/>
+      <c r="E298" s="19"/>
+      <c r="F298" s="19"/>
+      <c r="G298" s="19"/>
+      <c r="H298" s="19"/>
+      <c r="I298" s="19"/>
+      <c r="J298" s="19"/>
+      <c r="K298" s="19"/>
     </row>
     <row r="299" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B299" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="C299" s="28"/>
-      <c r="D299" s="28"/>
-      <c r="E299" s="28"/>
-      <c r="F299" s="28"/>
-      <c r="G299" s="28"/>
-      <c r="H299" s="28"/>
-      <c r="I299" s="28"/>
-      <c r="J299" s="28"/>
-      <c r="K299" s="28"/>
+      <c r="B299" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="C299" s="19"/>
+      <c r="D299" s="19"/>
+      <c r="E299" s="19"/>
+      <c r="F299" s="19"/>
+      <c r="G299" s="19"/>
+      <c r="H299" s="19"/>
+      <c r="I299" s="19"/>
+      <c r="J299" s="19"/>
+      <c r="K299" s="19"/>
     </row>
     <row r="301" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A301" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="B301" s="28"/>
-      <c r="C301" s="28"/>
-      <c r="D301" s="28"/>
-      <c r="E301" s="28"/>
-      <c r="F301" s="28"/>
-      <c r="G301" s="28"/>
-      <c r="H301" s="28"/>
-      <c r="I301" s="28"/>
-      <c r="J301" s="28"/>
-      <c r="K301" s="28"/>
+      <c r="A301" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="B301" s="19"/>
+      <c r="C301" s="19"/>
+      <c r="D301" s="19"/>
+      <c r="E301" s="19"/>
+      <c r="F301" s="19"/>
+      <c r="G301" s="19"/>
+      <c r="H301" s="19"/>
+      <c r="I301" s="19"/>
+      <c r="J301" s="19"/>
+      <c r="K301" s="19"/>
     </row>
     <row r="302" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A302" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="B302" s="28"/>
-      <c r="C302" s="28"/>
-      <c r="D302" s="28"/>
-      <c r="E302" s="28"/>
-      <c r="F302" s="28"/>
-      <c r="G302" s="28"/>
-      <c r="H302" s="28"/>
-      <c r="I302" s="28"/>
-      <c r="J302" s="28"/>
-      <c r="K302" s="28"/>
+      <c r="A302" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="B302" s="19"/>
+      <c r="C302" s="19"/>
+      <c r="D302" s="19"/>
+      <c r="E302" s="19"/>
+      <c r="F302" s="19"/>
+      <c r="G302" s="19"/>
+      <c r="H302" s="19"/>
+      <c r="I302" s="19"/>
+      <c r="J302" s="19"/>
+      <c r="K302" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A302:K302"/>
-    <mergeCell ref="C220:K220"/>
-    <mergeCell ref="C239:K239"/>
-    <mergeCell ref="C68:K68"/>
-    <mergeCell ref="C98:K98"/>
-    <mergeCell ref="C191:K191"/>
-    <mergeCell ref="B299:K299"/>
-    <mergeCell ref="C126:K126"/>
-    <mergeCell ref="C171:K171"/>
-    <mergeCell ref="A301:K301"/>
-    <mergeCell ref="C155:K155"/>
-    <mergeCell ref="C217:K217"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="C189:K189"/>
-    <mergeCell ref="C96:K96"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="B297:K297"/>
-    <mergeCell ref="C154:K154"/>
-    <mergeCell ref="C42:K42"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="C242:K242"/>
+    <mergeCell ref="C192:K192"/>
+    <mergeCell ref="C43:K43"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C271:K271"/>
+    <mergeCell ref="C152:K152"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A241:K241"/>
     <mergeCell ref="C71:K71"/>
@@ -5252,25 +5177,39 @@
     <mergeCell ref="C19:K19"/>
     <mergeCell ref="C292:K292"/>
     <mergeCell ref="A294:K294"/>
-    <mergeCell ref="B298:K298"/>
     <mergeCell ref="A3:K4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="C189:K189"/>
+    <mergeCell ref="C96:K96"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="B297:K297"/>
+    <mergeCell ref="C154:K154"/>
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="A9:K9"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="C99:K99"/>
     <mergeCell ref="C270:K270"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="C40:K40"/>
     <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A302:K302"/>
+    <mergeCell ref="C220:K220"/>
+    <mergeCell ref="C239:K239"/>
+    <mergeCell ref="C68:K68"/>
+    <mergeCell ref="C98:K98"/>
+    <mergeCell ref="C191:K191"/>
+    <mergeCell ref="B299:K299"/>
+    <mergeCell ref="C126:K126"/>
+    <mergeCell ref="C171:K171"/>
+    <mergeCell ref="A301:K301"/>
+    <mergeCell ref="C155:K155"/>
+    <mergeCell ref="C217:K217"/>
+    <mergeCell ref="B298:K298"/>
     <mergeCell ref="C124:K124"/>
     <mergeCell ref="C127:K127"/>
     <mergeCell ref="C173:K173"/>
-    <mergeCell ref="C242:K242"/>
-    <mergeCell ref="C192:K192"/>
-    <mergeCell ref="C43:K43"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C271:K271"/>
-    <mergeCell ref="C152:K152"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="E13:G13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H12" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>

--- a/finance-controlling/FB75-customer-credit-memo.xlsx
+++ b/finance-controlling/FB75-customer-credit-memo.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/24a7865e3124cb3d/Documents/PostNow/github-templates/finance-controlling/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="103" documentId="11_FBE209F5A48EC06889FF6FE448B231014C21C46A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C035CADC-17FC-44FB-B14B-487976A003C5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
